--- a/data/structured_data/郑州轻工业大学教务流程及校园服务核心信息.xlsx
+++ b/data/structured_data/郑州轻工业大学教务流程及校园服务核心信息.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18350" windowHeight="8200"/>
+    <workbookView windowWidth="12220" windowHeight="8200"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
